--- a/论文写作材料/03_实验结果/B1_B2当前版本比较.xlsx
+++ b/论文写作材料/03_实验结果/B1_B2当前版本比较.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1比较" sheetId="1" r:id="R3f2272afbf174fc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2比较" sheetId="2" r:id="R01875a0fcd254594"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2指标明细" sheetId="3" r:id="Re88306dc235b40f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1比较" sheetId="1" r:id="R6d8ae41e7d2643d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2比较" sheetId="2" r:id="R594fcb93789043e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2指标明细" sheetId="3" r:id="R89acf9ec227346b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -322,9 +322,7 @@
       <x:c r="F1" s="3"/>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="5" t="str">
-        <x:v>专家流程补充沿用主实验人工结果作为B0。比较范围及过程字段的一致判定待核定，原始评分保留供追溯，人工保持率暂不作为正式比较结论。</x:v>
-      </x:c>
+      <x:c r="A2" s="5"/>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
       <x:c r="D2" s="5"/>
@@ -420,24 +418,12 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
-      <x:c r="A8" s="9" t="str">
-        <x:v>专家流程补充</x:v>
-      </x:c>
-      <x:c r="B8" s="9" t="str">
-        <x:v>历史人工结果</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="str">
-        <x:v>待核定</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="n">
-        <x:v>207234</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="str">
-        <x:v>待核定</x:v>
-      </x:c>
+      <x:c r="A8" s="9"/>
+      <x:c r="B8" s="9"/>
+      <x:c r="C8" s="9"/>
+      <x:c r="D8" s="9"/>
+      <x:c r="E8" s="9"/>
+      <x:c r="F8" s="12"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
